--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:15</t>
+    <t xml:space="preserve">2026-09-09 23:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:09</t>
+    <t xml:space="preserve">2026-09-17 14:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:06</t>
+    <t xml:space="preserve">2026-09-23 12:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1500,7 +1500,9 @@
       <c r="C53" s="2" t="n">
         <v>13505</v>
       </c>
-      <c r="D53" s="2"/>
+      <c r="D53" s="2" t="n">
+        <v>2020</v>
+      </c>
       <c r="E53" s="2"/>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:35</t>
+    <t xml:space="preserve">2026-10-02 14:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:03</t>
+    <t xml:space="preserve">2026-10-05 10:44</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -790,7 +790,7 @@
         <v>2020</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>503167.12</v>
+        <v>503167.13</v>
       </c>
     </row>
     <row r="12">
@@ -875,7 +875,7 @@
         <v>2020</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>374190.62</v>
+        <v>374190.63</v>
       </c>
     </row>
     <row r="17">
@@ -977,7 +977,7 @@
         <v>2020</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>334229.12</v>
+        <v>334229.13</v>
       </c>
     </row>
     <row r="23">
@@ -1062,7 +1062,7 @@
         <v>2020</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>327239.12</v>
+        <v>327239.13</v>
       </c>
     </row>
     <row r="28">
@@ -1096,7 +1096,7 @@
         <v>2020</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>312523.12</v>
+        <v>312523.13</v>
       </c>
     </row>
     <row r="30">
@@ -1181,7 +1181,7 @@
         <v>2020</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>296155.12</v>
+        <v>296155.13</v>
       </c>
     </row>
     <row r="35">
